--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="197">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,13 +428,7 @@
     <t>Statut de la ligne de prescription</t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -1500,7 +1494,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2648,31 +2642,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>74</v>
@@ -2686,10 +2680,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2715,10 +2709,10 @@
         <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2769,7 +2763,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -2786,10 +2780,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2815,10 +2809,10 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2869,7 +2863,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -2886,10 +2880,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2912,13 +2906,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2969,7 +2963,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -2986,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3012,13 +3006,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3069,7 +3063,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3086,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3112,13 +3106,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3145,10 +3139,10 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3169,7 +3163,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3186,10 +3180,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3215,10 +3209,10 @@
         <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3269,7 +3263,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3286,10 +3280,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3312,13 +3306,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3369,7 +3363,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3386,10 +3380,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3412,13 +3406,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3469,7 +3463,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3486,10 +3480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3512,13 +3506,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3569,7 +3563,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -3586,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3612,13 +3606,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3669,7 +3663,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -3686,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3715,10 +3709,10 @@
         <v>80</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3769,7 +3763,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -3786,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3812,13 +3806,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3848,10 +3842,10 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3869,7 +3863,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -3886,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3912,13 +3906,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3969,7 +3963,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -3986,10 +3980,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4012,13 +4006,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4069,7 +4063,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4086,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4112,13 +4106,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4169,7 +4163,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4186,10 +4180,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4215,10 +4209,10 @@
         <v>80</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4269,7 +4263,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4286,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4312,13 +4306,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4369,7 +4363,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4386,10 +4380,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4412,13 +4406,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4469,7 +4463,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -4486,10 +4480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4512,13 +4506,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4569,7 +4563,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -4586,10 +4580,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4612,13 +4606,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4669,7 +4663,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4686,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4712,13 +4706,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4769,7 +4763,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4786,10 +4780,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4812,13 +4806,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4869,7 +4863,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4886,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4912,13 +4906,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4969,7 +4963,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
